--- a/未消费客户明细/销售人员.xlsx
+++ b/未消费客户明细/销售人员.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$922</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$923</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="1096">
   <si>
     <t>公司名称</t>
   </si>
@@ -3331,6 +3331,12 @@
   </si>
   <si>
     <t>林伶伶</t>
+  </si>
+  <si>
+    <t>漳州市龙文区金泰亨商务咨询服务部</t>
+  </si>
+  <si>
+    <t>叁柒贰壹（泉州）建筑设计有限公司</t>
   </si>
 </sst>
 </file>
@@ -3339,8 +3345,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -3365,23 +3371,29 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3389,15 +3401,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3417,16 +3430,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3442,25 +3447,47 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3480,30 +3507,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3524,13 +3530,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3548,13 +3584,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3566,7 +3608,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3578,7 +3650,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3590,13 +3662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3608,7 +3674,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3620,61 +3698,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3686,25 +3710,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3737,22 +3743,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3768,6 +3759,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3789,11 +3791,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3801,8 +3816,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3821,25 +3836,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3848,133 +3854,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4371,7 +4377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD923"/>
+  <dimension ref="A1:XFD925"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="23.375" style="1" customWidth="1"/>
@@ -30910,8 +30916,30 @@
         <v>11</v>
       </c>
     </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B924" s="2">
+        <v>45153</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B925" s="2">
+        <v>45153</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C922">
+  <autoFilter ref="A1:C923">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A881:A885">

--- a/未消费客户明细/销售人员.xlsx
+++ b/未消费客户明细/销售人员.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$923</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$925</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="1098">
   <si>
     <t>公司名称</t>
   </si>
@@ -3337,6 +3337,12 @@
   </si>
   <si>
     <t>叁柒贰壹（泉州）建筑设计有限公司</t>
+  </si>
+  <si>
+    <t>福建宜顺禾贸易有限责任公司</t>
+  </si>
+  <si>
+    <t>泉州大大交通工程有限公司</t>
   </si>
 </sst>
 </file>
@@ -3346,8 +3352,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -3371,35 +3377,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -3408,16 +3385,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3425,6 +3402,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3439,7 +3423,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3448,6 +3439,45 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3469,14 +3499,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -3484,32 +3506,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3536,7 +3542,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3554,109 +3692,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3674,43 +3710,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3739,11 +3745,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3763,17 +3775,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3785,15 +3786,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3815,6 +3807,26 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -3822,17 +3834,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3842,10 +3848,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3854,133 +3860,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4377,7 +4383,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD925"/>
+  <dimension ref="A1:XFD927"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="23.375" style="1" customWidth="1"/>
@@ -30938,26 +30944,51 @@
         <v>6</v>
       </c>
     </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B926" s="2">
+        <v>45155</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B927" s="2">
+        <v>45155</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C923">
+  <autoFilter ref="A1:C925">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A881:A885">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A926:A928">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A880 A886:A913 A915:A919 A924:A925 A929:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A920 C920">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A880 A886:A913 A915:A919 A924:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A920 C920">
+  <conditionalFormatting sqref="A921:A922 C921:C922">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A921:A922 C921:C922">
+  <conditionalFormatting sqref="A923 C923">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A923 C923">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/未消费客户明细/销售人员.xlsx
+++ b/未消费客户明细/销售人员.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$925</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1015</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1196">
   <si>
     <t>公司名称</t>
   </si>
@@ -3343,6 +3343,300 @@
   </si>
   <si>
     <t>泉州大大交通工程有限公司</t>
+  </si>
+  <si>
+    <t>厦门鑫川晟印务有限公司</t>
+  </si>
+  <si>
+    <t>厦门天蓬网络科技有限公司</t>
+  </si>
+  <si>
+    <t>上海浪湖泵业制造有限公司</t>
+  </si>
+  <si>
+    <t>扬果（厦门）信息科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门朋龙厦工程机械有限公司</t>
+  </si>
+  <si>
+    <t>福建省南象投资集团有限公司</t>
+  </si>
+  <si>
+    <t>厦门数之能科技有限公司</t>
+  </si>
+  <si>
+    <t>漳州市龙文区铭诚信息咨询服务部</t>
+  </si>
+  <si>
+    <t>厦门一艺通工业设备有限公司</t>
+  </si>
+  <si>
+    <t>泉州市云畅信息科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门九凤文化传媒有限公司</t>
+  </si>
+  <si>
+    <t>厦门盛之康农业开发有限公司</t>
+  </si>
+  <si>
+    <t>漳州芗城呀哚口腔诊所</t>
+  </si>
+  <si>
+    <t>晋江市池店镇胥玲风鞋服商行</t>
+  </si>
+  <si>
+    <t>安溪博力石材工具有限公司</t>
+  </si>
+  <si>
+    <t>厦门赛尔吉亚医学检验所有限公司</t>
+  </si>
+  <si>
+    <t>特士勒智能检测系统（厦门）有限公司</t>
+  </si>
+  <si>
+    <t>漳浦县官浔镇优客苗木场</t>
+  </si>
+  <si>
+    <t>厦门骏铠信息科技有限公司</t>
+  </si>
+  <si>
+    <t>张馨如</t>
+  </si>
+  <si>
+    <t>漳州芗城医肤堂皮肤专科门诊部</t>
+  </si>
+  <si>
+    <t>福建厦兴重工机械有限公司</t>
+  </si>
+  <si>
+    <t>泉州福狮特建筑工程有限公司</t>
+  </si>
+  <si>
+    <t>厦门利娅财务咨询有限公司</t>
+  </si>
+  <si>
+    <t>厦门博拉福研学教育科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门思明瑞丽嘉整形外科门诊部</t>
+  </si>
+  <si>
+    <t>漳州市珠港物流有限公司</t>
+  </si>
+  <si>
+    <t>厦门祺佑信息科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门市畅达骏旅游运输有限公司</t>
+  </si>
+  <si>
+    <t>苏阀安全设备（福建）有限公司</t>
+  </si>
+  <si>
+    <t>福建吉扬璟世律师事务所</t>
+  </si>
+  <si>
+    <t>厦门茶叶进出口有限公司</t>
+  </si>
+  <si>
+    <t>厦门码创智美科技有限公司 </t>
+  </si>
+  <si>
+    <t>厦门乔与知科技有限公司</t>
+  </si>
+  <si>
+    <t>赞童（厦门）科技有限公司</t>
+  </si>
+  <si>
+    <t>福建省如顺生物科技有限公司</t>
+  </si>
+  <si>
+    <t>漳州市蓝藻网络科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门凯斯勒咨询服务有限公司</t>
+  </si>
+  <si>
+    <t>晋江市安海镇世存钟表店</t>
+  </si>
+  <si>
+    <t>周逸鸣</t>
+  </si>
+  <si>
+    <t>惠安县锦艺服装厂</t>
+  </si>
+  <si>
+    <t>厦门禾远商贸有限公司</t>
+  </si>
+  <si>
+    <t>胡成</t>
+  </si>
+  <si>
+    <t>泉州市医鹭好健康管理有限责任公司</t>
+  </si>
+  <si>
+    <t>厦门蚂蚁搬砖网络科技有限公司</t>
+  </si>
+  <si>
+    <t>易成功（厦门）信息科技有限公司</t>
+  </si>
+  <si>
+    <t>杨超</t>
+  </si>
+  <si>
+    <t>厦门众星悦网络科技有限公司</t>
+  </si>
+  <si>
+    <t>达瑞（泉州）新能源科技有限公司</t>
+  </si>
+  <si>
+    <t>泉州浩玮装饰工程有限公司</t>
+  </si>
+  <si>
+    <t>厦门时拓众创空间管理服务有限公司</t>
+  </si>
+  <si>
+    <t>柯智楷</t>
+  </si>
+  <si>
+    <t>金牌厨柜家居科技股份有限公司</t>
+  </si>
+  <si>
+    <t>晋江市陈埭镇顺顺废品回收站</t>
+  </si>
+  <si>
+    <t>厦门盛妆化妆品有限公司</t>
+  </si>
+  <si>
+    <t>厦门市翔安区翔绿源苗圃</t>
+  </si>
+  <si>
+    <t>厦门芒读科技服务有限公司</t>
+  </si>
+  <si>
+    <t>晋江市池店镇赛虎货运代理服务部</t>
+  </si>
+  <si>
+    <t>厦门瑞喜汽车租赁有限公司</t>
+  </si>
+  <si>
+    <t>许晶铭</t>
+  </si>
+  <si>
+    <t>厦门有鱼么文化传媒有限公司</t>
+  </si>
+  <si>
+    <t>福建荣金供应链管理有限公司</t>
+  </si>
+  <si>
+    <t>福建碧湖教育科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门势拓伺服科技股份有限公司</t>
+  </si>
+  <si>
+    <t>福建甜芒科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门市天晴了教育咨询有限公司</t>
+  </si>
+  <si>
+    <t>章朝雄</t>
+  </si>
+  <si>
+    <t>厦门模优科技有限公司</t>
+  </si>
+  <si>
+    <t>福建三冠陶瓷科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门小工单科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门美弗仪自动化科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门净邦生物科技有限公司</t>
+  </si>
+  <si>
+    <t>泉州恒锐再生资源有限公司</t>
+  </si>
+  <si>
+    <t>福建泉州市米柚装饰工程有限公司</t>
+  </si>
+  <si>
+    <t>苏超艺</t>
+  </si>
+  <si>
+    <t>福建泉成机械有限公司</t>
+  </si>
+  <si>
+    <t>成信集成科技股份有限公司</t>
+  </si>
+  <si>
+    <t>厦门魔科网络科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门都链科技有限公司</t>
+  </si>
+  <si>
+    <t>厦门君盛达会务服务有限公司</t>
+  </si>
+  <si>
+    <t>厦门寰太展览服务有限公司</t>
+  </si>
+  <si>
+    <t>福建省冲霄建筑工程有限公司</t>
+  </si>
+  <si>
+    <t>厦门盈亦自动化科技有限公司</t>
+  </si>
+  <si>
+    <t>晋江闽粤达物流有限公司</t>
+  </si>
+  <si>
+    <t>云霄县嘉安服装店</t>
+  </si>
+  <si>
+    <t>德化县天云陶瓷工作室</t>
+  </si>
+  <si>
+    <t>厦门芯曙光科技有限公司</t>
+  </si>
+  <si>
+    <t>漳州创诚家政服务有限公司</t>
+  </si>
+  <si>
+    <t>泉州市将肯网络科技有限公司</t>
+  </si>
+  <si>
+    <t>傅锦鸿</t>
+  </si>
+  <si>
+    <t>漳州市鸿瑞物流有限公司</t>
+  </si>
+  <si>
+    <t>厦门管账婆企业服务有限公司</t>
+  </si>
+  <si>
+    <t>漳州顶楼木业有限公司</t>
+  </si>
+  <si>
+    <t>庄舒鹏</t>
+  </si>
+  <si>
+    <t>厦门推闻网络科技有限公司</t>
+  </si>
+  <si>
+    <t>晋江市国材商标事务所</t>
+  </si>
+  <si>
+    <t>漳州市金斗云汽车服务有限公司</t>
+  </si>
+  <si>
+    <t>厦门首游国际旅行社有限公司</t>
   </si>
 </sst>
 </file>
@@ -3351,9 +3645,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -3377,6 +3671,36 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -3385,8 +3709,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3401,93 +3763,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3506,8 +3784,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3515,7 +3801,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3536,72 +3830,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3614,7 +3842,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3626,7 +3926,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3638,13 +3986,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3656,67 +4004,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3746,21 +4040,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -3775,16 +4054,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -3807,11 +4106,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3825,20 +4122,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3848,10 +4142,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3860,133 +4154,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4383,7 +4677,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD927"/>
+  <dimension ref="A1:XFD1017"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="23.375" style="1" customWidth="1"/>
@@ -30966,29 +31260,1052 @@
         <v>1077</v>
       </c>
     </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B928" s="2">
+        <v>45156</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B929" s="2">
+        <v>45156</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B930" s="2">
+        <v>45156</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B931" s="2">
+        <v>45159</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B932" s="2">
+        <v>45159</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B933" s="2">
+        <v>45159</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B934" s="2">
+        <v>45160</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B935" s="2">
+        <v>45160</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B936" s="2">
+        <v>45160</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B937" s="2">
+        <v>45160</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B938" s="2">
+        <v>45161</v>
+      </c>
+      <c r="C938" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B939" s="2">
+        <v>45162</v>
+      </c>
+      <c r="C939" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B940" s="2">
+        <v>45162</v>
+      </c>
+      <c r="C940" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B941" s="2">
+        <v>45162</v>
+      </c>
+      <c r="C941" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B942" s="2">
+        <v>45162</v>
+      </c>
+      <c r="C942" s="3" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B943" s="2">
+        <v>45163</v>
+      </c>
+      <c r="C943" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B944" s="2">
+        <v>45163</v>
+      </c>
+      <c r="C944" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B945" s="2">
+        <v>45164</v>
+      </c>
+      <c r="C945" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B946" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C946" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B947" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C947" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B948" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C948" s="3" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3">
+      <c r="A949" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B949" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C949" s="3" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3">
+      <c r="A950" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B950" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C950" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3">
+      <c r="A951" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B951" s="2">
+        <v>45166</v>
+      </c>
+      <c r="C951" s="3" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3">
+      <c r="A952" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B952" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C952" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3">
+      <c r="A953" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B953" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C953" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3">
+      <c r="A954" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B954" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C954" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3">
+      <c r="A955" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B955" s="2">
+        <v>45167</v>
+      </c>
+      <c r="C955" s="3" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3">
+      <c r="A956" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B956" s="2">
+        <v>45168</v>
+      </c>
+      <c r="C956" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3">
+      <c r="A957" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B957" s="2">
+        <v>45168</v>
+      </c>
+      <c r="C957" s="3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3">
+      <c r="A958" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B958" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C958" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3">
+      <c r="A959" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B959" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C959" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3">
+      <c r="A960" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B960" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C960" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3">
+      <c r="A961" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B961" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C961" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3">
+      <c r="A962" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B962" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C962" s="3" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3">
+      <c r="A963" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B963" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C963" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3">
+      <c r="A964" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B964" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C964" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3">
+      <c r="A965" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B965" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C965" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3">
+      <c r="A966" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B966" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C966" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3">
+      <c r="A967" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B967" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C967" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3">
+      <c r="A968" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B968" s="2">
+        <v>45173</v>
+      </c>
+      <c r="C968" s="3" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3">
+      <c r="A969" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B969" s="2">
+        <v>45173</v>
+      </c>
+      <c r="C969" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3">
+      <c r="A970" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B970" s="2">
+        <v>45174</v>
+      </c>
+      <c r="C970" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3">
+      <c r="A971" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B971" s="2">
+        <v>45174</v>
+      </c>
+      <c r="C971" s="3" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3">
+      <c r="A972" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B972" s="2">
+        <v>45174</v>
+      </c>
+      <c r="C972" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3">
+      <c r="A973" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B973" s="2">
+        <v>45174</v>
+      </c>
+      <c r="C973" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3">
+      <c r="A974" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B974" s="2">
+        <v>45174</v>
+      </c>
+      <c r="C974" s="3" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3">
+      <c r="A975" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B975" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C975" s="3" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3">
+      <c r="A976" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B976" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C976" s="3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3">
+      <c r="A977" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B977" s="2">
+        <v>45175</v>
+      </c>
+      <c r="C977" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3">
+      <c r="A978" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B978" s="2">
+        <v>45176</v>
+      </c>
+      <c r="C978" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3">
+      <c r="A979" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B979" s="2">
+        <v>45176</v>
+      </c>
+      <c r="C979" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3">
+      <c r="A980" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B980" s="2">
+        <v>45177</v>
+      </c>
+      <c r="C980" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3">
+      <c r="A981" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B981" s="2">
+        <v>45176</v>
+      </c>
+      <c r="C981" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3">
+      <c r="A982" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B982" s="2">
+        <v>45177</v>
+      </c>
+      <c r="C982" s="3" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3">
+      <c r="A983" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B983" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C983" s="3" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3">
+      <c r="A984" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B984" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3">
+      <c r="A985" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B985" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C985" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3">
+      <c r="A986" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B986" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C986" s="3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3">
+      <c r="A987" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B987" s="2">
+        <v>45180</v>
+      </c>
+      <c r="C987" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3">
+      <c r="A988" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B988" s="2">
+        <v>45181</v>
+      </c>
+      <c r="C988" s="3" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3">
+      <c r="A989" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B989" s="2">
+        <v>45181</v>
+      </c>
+      <c r="C989" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3">
+      <c r="A990" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B990" s="2">
+        <v>45182</v>
+      </c>
+      <c r="C990" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3">
+      <c r="A991" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B991" s="2">
+        <v>45182</v>
+      </c>
+      <c r="C991" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3">
+      <c r="A992" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B992" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C992" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3">
+      <c r="A993" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B993" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3">
+      <c r="A994" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B994" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C994" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3">
+      <c r="A995" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B995" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C995" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3">
+      <c r="A996" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B996" s="2">
+        <v>45183</v>
+      </c>
+      <c r="C996" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3">
+      <c r="A997" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B997" s="2">
+        <v>45184</v>
+      </c>
+      <c r="C997" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3">
+      <c r="A998" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B998" s="2">
+        <v>45187</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3">
+      <c r="A999" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B999" s="2">
+        <v>45187</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3">
+      <c r="A1000" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1000" s="2">
+        <v>45187</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3">
+      <c r="A1001" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1001" s="2">
+        <v>45187</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3">
+      <c r="A1002" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1002" s="2">
+        <v>45188</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3">
+      <c r="A1003" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B1003" s="2">
+        <v>45188</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3">
+      <c r="A1004" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1004" s="2">
+        <v>45189</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3">
+      <c r="A1005" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1005" s="2">
+        <v>45189</v>
+      </c>
+      <c r="C1005" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3">
+      <c r="A1006" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B1006" s="2">
+        <v>45189</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3">
+      <c r="A1007" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B1007" s="2">
+        <v>45189</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3">
+      <c r="A1008" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1008" s="2">
+        <v>45190</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3">
+      <c r="A1009" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1009" s="2">
+        <v>45190</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3">
+      <c r="A1010" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1010" s="2">
+        <v>45191</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3">
+      <c r="A1011" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1011" s="2">
+        <v>45192</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3">
+      <c r="A1012" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1012" s="2">
+        <v>45192</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3">
+      <c r="A1013" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1013" s="2">
+        <v>45194</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3">
+      <c r="A1014" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1014" s="2">
+        <v>45194</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3">
+      <c r="A1015" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B1015" s="2">
+        <v>45194</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3">
+      <c r="A1016" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B1016" s="2">
+        <v>45195</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3">
+      <c r="A1017" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1017" s="2">
+        <v>45195</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C925">
+  <autoFilter ref="A1:C1015">
     <extLst/>
   </autoFilter>
+  <conditionalFormatting sqref="A943">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A881:A885">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A926:A927">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A928:A933">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A934:A936">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A937:A938">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A939:A942">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A944:A950">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A951:A957">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A926:A928">
+  <conditionalFormatting sqref="A958:A962">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A963:A966">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A967:A969">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A970:A972">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A880 A886:A913 A915:A919 A924:A925 A929:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="A1:A880 A886:A913 A915:A919 A924:A925 A1018:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A920 C920">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A921:A922 C921:C922">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A923 C923">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
